--- a/artfynd/A 58350-2025 artfynd.xlsx
+++ b/artfynd/A 58350-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132019651</v>
       </c>
       <c r="B2" t="n">
-        <v>97661</v>
+        <v>97662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58350-2025 artfynd.xlsx
+++ b/artfynd/A 58350-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132019651</v>
       </c>
       <c r="B2" t="n">
-        <v>97662</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58350-2025 artfynd.xlsx
+++ b/artfynd/A 58350-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132019651</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58350-2025 artfynd.xlsx
+++ b/artfynd/A 58350-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132019651</v>
       </c>
       <c r="B2" t="n">
-        <v>97669</v>
+        <v>97705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58350-2025 artfynd.xlsx
+++ b/artfynd/A 58350-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132019651</v>
       </c>
       <c r="B2" t="n">
-        <v>97710</v>
+        <v>97713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58350-2025 artfynd.xlsx
+++ b/artfynd/A 58350-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132019651</v>
+        <v>88697140</v>
       </c>
       <c r="B2" t="n">
-        <v>97733</v>
+        <v>92732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>2014</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Näs, Fjällfota, Sk</t>
+          <t>Näs, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>393672</v>
+        <v>393687</v>
       </c>
       <c r="R2" t="n">
-        <v>6155416</v>
+        <v>6155543</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2020-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2020-10-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,23 +761,125 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Granplantering på myrmark</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Magnus Karlsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Magnus Karlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132019651</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97810</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Näs, Fjällfota, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>393672</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6155416</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hyby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Granplantering på myrmark</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Alex Regnér</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Alex Regnér</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58350-2025 artfynd.xlsx
+++ b/artfynd/A 58350-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88697140</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,8 +890,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132019651</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>